--- a/data/trans_dic/IP09-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP09-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen actualmente esa dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Menores que padecen actualmente esa dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,62</t>
+          <t>0,0; 44,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,74; 68,46</t>
+          <t>27,42; 68,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,04; 61,21</t>
+          <t>6,82; 59,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,53; 94,24</t>
+          <t>27,22; 93,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 44,22</t>
+          <t>5,55; 40,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,35; 61,19</t>
+          <t>18,61; 60,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,88; 66,21</t>
+          <t>14,19; 66,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 43,54</t>
+          <t>4,58; 45,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 34,28</t>
+          <t>4,04; 35,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,2; 59,42</t>
+          <t>29,94; 59,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,37; 53,24</t>
+          <t>16,52; 53,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,31; 74,08</t>
+          <t>18,75; 73,01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,31; 74,9</t>
+          <t>24,17; 74,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,07; 67,06</t>
+          <t>22,3; 66,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,67; 100,0</t>
+          <t>32,71; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,57</t>
+          <t>0,0; 53,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 38,84</t>
+          <t>5,44; 38,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,34; 69,53</t>
+          <t>23,05; 69,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>18,38; 100,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,82; 80,21</t>
+          <t>21,58; 79,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,68; 48,36</t>
+          <t>16,4; 48,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,88; 60,96</t>
+          <t>29,42; 61,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,62; 91,3</t>
+          <t>36,26; 91,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,2; 60,85</t>
+          <t>19,03; 58,94</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,77</t>
+          <t>0,0; 62,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,96; 52,96</t>
+          <t>7,11; 54,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,34</t>
+          <t>0,0; 86,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,77; 52,57</t>
+          <t>0,0; 51,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,78; 74,81</t>
+          <t>12,04; 74,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,37; 65,67</t>
+          <t>10,35; 66,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,79; 66,46</t>
+          <t>13,88; 69,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,88; 54,75</t>
+          <t>7,65; 53,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,15; 48,85</t>
+          <t>12,61; 48,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,43</t>
+          <t>0,0; 51,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,55; 54,09</t>
+          <t>15,14; 52,61</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,12</t>
+          <t>0,0; 36,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 85,5</t>
+          <t>0,0; 85,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,68; 67,5</t>
+          <t>12,21; 64,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,42; 61,12</t>
+          <t>7,8; 60,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,02; 64,37</t>
+          <t>8,11; 63,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,96</t>
+          <t>0,0; 41,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,43; 70,28</t>
+          <t>13,45; 66,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,62</t>
+          <t>0,0; 30,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 41,82</t>
+          <t>4,38; 40,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,04; 45,24</t>
+          <t>5,23; 43,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,98; 59,94</t>
+          <t>21,03; 56,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 31,94</t>
+          <t>2,28; 31,38</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,65</t>
+          <t>0,0; 73,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,53</t>
+          <t>0,0; 61,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,18</t>
+          <t>0,0; 64,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,29; 85,66</t>
+          <t>14,29; 85,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,35; 84,92</t>
+          <t>27,81; 84,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>40,78; 100,0</t>
+          <t>38,95; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,76; 65,47</t>
+          <t>13,93; 66,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,94; 65,84</t>
+          <t>22,72; 65,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,62; 79,45</t>
+          <t>23,71; 80,08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1421,64 +1422,64 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,58</t>
+          <t>0,0; 63,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37,03; 91,21</t>
+          <t>35,21; 91,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,25</t>
+          <t>0,0; 63,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,38; 53,11</t>
+          <t>7,35; 53,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,3; 100,0</t>
+          <t>51,61; 100,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,68; 51,8</t>
+          <t>10,51; 52,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,98; 66,19</t>
+          <t>10,08; 72,75</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,41; 47,89</t>
+          <t>9,38; 48,01</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55,44; 93,25</t>
+          <t>53,17; 93,34</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,86; 41,79</t>
+          <t>7,03; 39,45</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,85; 68,73</t>
+          <t>25,8; 68,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,09</t>
+          <t>0,0; 55,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,05; 59,94</t>
+          <t>12,07; 61,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,58; 60,13</t>
+          <t>21,49; 62,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,06; 47,95</t>
+          <t>12,36; 46,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,77; 51,21</t>
+          <t>6,88; 50,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,09; 52,99</t>
+          <t>14,88; 54,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,06; 40,59</t>
+          <t>12,94; 40,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23,19; 51,21</t>
+          <t>21,97; 49,85</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,92; 39,54</t>
+          <t>7,9; 40,25</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,65; 46,75</t>
+          <t>18,54; 48,24</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,31; 52,38</t>
+          <t>10,59; 54,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,35; 39,94</t>
+          <t>10,02; 39,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,53; 62,2</t>
+          <t>10,37; 62,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36,55; 88,18</t>
+          <t>33,19; 87,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,7; 46,87</t>
+          <t>14,99; 45,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,47; 47,08</t>
+          <t>14,93; 44,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,88; 92,64</t>
+          <t>41,1; 92,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19,41; 80,83</t>
+          <t>18,76; 81,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,19; 42,51</t>
+          <t>17,09; 42,52</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15,83; 37,74</t>
+          <t>15,67; 37,24</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34,38; 72,43</t>
+          <t>32,94; 72,78</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>37,36; 77,43</t>
+          <t>38,33; 78,44</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14,34; 32,43</t>
+          <t>15,2; 33,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26,05; 42,84</t>
+          <t>26,84; 43,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29,68; 52,38</t>
+          <t>29,11; 51,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26,7; 56,99</t>
+          <t>27,69; 58,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,67; 36,82</t>
+          <t>21,42; 37,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,05; 42,65</t>
+          <t>26,02; 41,34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,37; 58,14</t>
+          <t>34,37; 56,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,61; 39,25</t>
+          <t>19,14; 39,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,95; 33,06</t>
+          <t>20,57; 32,23</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28,93; 40,34</t>
+          <t>28,31; 40,06</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35,85; 52,0</t>
+          <t>34,9; 50,98</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25,71; 42,58</t>
+          <t>25,88; 43,54</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen actualmente esa dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6999</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1914</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8775</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7216</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3212</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2478</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2626</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14215</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5126</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>11253</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2565</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4021; 9983</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>472; 4129</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3600; 12312</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>630; 4633</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3326; 10891</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1275; 6016</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>628; 6235</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>694; 6016</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9740; 19428</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2628; 8559</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5051; 19668</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4757</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5228</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3028</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1599</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1957</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5509</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4530</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>6713</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>10737</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5033</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6129</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2438; 7557</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2679; 8009</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1188; 3632</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4127</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>641; 4555</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2745; 8330</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>626; 3403</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1891; 6942</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3587; 10531</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>7039; 14706</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2551; 6428</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3131; 9696</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2116</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1654</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1874</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3240</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2665</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4894</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3202</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>658; 5049</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4026</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3697</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>607; 3767</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>637; 4069</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1179; 5944</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>777; 5471</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1944; 7500</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3822</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2376; 8259</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1552</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3413</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2720</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3757</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1691</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2625</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2207</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7170</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>4411</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2385</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3588</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1114; 5847</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>724; 5572</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>606; 4750</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3225</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1286; 6339</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6697</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>616; 5700</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>627; 5251</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3931; 10573</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>718; 9881</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1551</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5453</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3563</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3657</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>6328</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>4025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3857</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3295</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2071</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>698; 4185</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2544; 7744</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1617; 4151</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1410; 6708</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3296; 9564</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1743; 5887</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1482</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1273</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2063</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>6907</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>3219</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2678</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3545</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>12171</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3219</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2076</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3707</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2592; 6714</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3189</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>666; 4847</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>4107; 7957</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1214; 6055</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>715; 5160</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1396; 7145</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>8145; 14299</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1106; 6205</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>6141</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>5973</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>4870</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>6836</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>5973</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>11011</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3325</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>9937</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>3346; 8913</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4080</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1166; 5976</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3237; 9433</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2206; 8273</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>632; 4632</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>3289; 12112</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>3217; 9961</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>6770; 15363</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>1310; 6678</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>5890; 15321</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>3171</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>4004</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2587</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5591</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>6733</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>6495</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>5910</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>4043</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>9904</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>10499</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>8497</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>9634</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1218; 6320</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>1861; 7318</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>770; 4613</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2765; 7306</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>3425; 10354</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>3385; 10172</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>3439; 7736</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>1512; 6577</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>5870; 14606</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>6462; 15361</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5201; 11491</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>6284; 12858</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>12800</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>28397</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>19077</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>23901</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>24042</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>34252</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>23775</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>29601</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>36842</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>62649</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>42852</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>53502</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>8551; 18823</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>22240; 35877</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>13716; 24245</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>17385; 37000</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>17885; 31518</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>26651; 42342</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>17685; 29248</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>18953; 38918</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>28746; 45033</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>52464; 74221</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>34396; 50248</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>41883; 70448</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP09-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP09-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,03</t>
+          <t>0,0; 44,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,42; 68,09</t>
+          <t>27,1; 69,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 59,65</t>
+          <t>6,37; 62,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,22; 93,07</t>
+          <t>26,63; 95,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 40,82</t>
+          <t>5,48; 42,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,61; 60,95</t>
+          <t>20,73; 61,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,19; 66,95</t>
+          <t>12,91; 66,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 45,48</t>
+          <t>4,59; 41,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 35,03</t>
+          <t>3,97; 32,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,94; 59,72</t>
+          <t>29,18; 58,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,52; 53,8</t>
+          <t>16,13; 53,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,75; 73,01</t>
+          <t>19,92; 73,18</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,17; 74,92</t>
+          <t>24,84; 74,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,3; 66,67</t>
+          <t>21,94; 67,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,71; 100,0</t>
+          <t>33,54; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,66</t>
+          <t>0,0; 54,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 38,64</t>
+          <t>5,46; 39,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,05; 69,94</t>
+          <t>22,09; 69,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,38; 100,0</t>
+          <t>17,9; 100,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,58; 79,23</t>
+          <t>23,73; 80,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,4; 48,15</t>
+          <t>17,18; 49,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,42; 61,47</t>
+          <t>29,99; 61,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,26; 91,37</t>
+          <t>42,45; 91,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,03; 58,94</t>
+          <t>18,78; 59,1</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,52</t>
+          <t>0,0; 61,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 54,56</t>
+          <t>6,88; 53,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 86,46</t>
+          <t>0,0; 80,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,32</t>
+          <t>6,53; 53,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,35; 66,1</t>
+          <t>10,43; 66,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,88; 69,98</t>
+          <t>13,08; 71,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,65; 53,82</t>
+          <t>7,73; 55,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,61; 48,67</t>
+          <t>9,33; 49,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,88</t>
+          <t>0,0; 59,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,14; 52,61</t>
+          <t>13,31; 52,76</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,08</t>
+          <t>0,0; 34,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 85,08</t>
+          <t>0,0; 73,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,21; 64,07</t>
+          <t>14,31; 67,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,8; 60,01</t>
+          <t>8,58; 63,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 63,53</t>
+          <t>8,19; 63,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,59</t>
+          <t>0,0; 38,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,45; 66,27</t>
+          <t>15,19; 67,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,16</t>
+          <t>0,0; 29,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 40,46</t>
+          <t>4,83; 40,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 43,86</t>
+          <t>5,33; 44,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,03; 56,56</t>
+          <t>21,16; 58,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 31,38</t>
+          <t>2,39; 32,51</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,64</t>
+          <t>0,0; 73,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,54</t>
+          <t>0,0; 63,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,71</t>
+          <t>0,0; 50,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,81; 84,64</t>
+          <t>29,7; 84,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>38,95; 100,0</t>
+          <t>44,05; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,93; 66,27</t>
+          <t>13,58; 64,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,72; 65,93</t>
+          <t>22,78; 65,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,71; 80,08</t>
+          <t>26,12; 78,79</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,69</t>
+          <t>0,0; 63,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,21; 91,19</t>
+          <t>42,68; 91,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,57</t>
+          <t>0,0; 63,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,35; 53,49</t>
+          <t>7,28; 52,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51,61; 100,0</t>
+          <t>52,18; 100,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,51; 52,43</t>
+          <t>11,88; 51,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,08; 72,75</t>
+          <t>9,9; 73,26</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,38; 48,01</t>
+          <t>9,43; 47,1</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>53,17; 93,34</t>
+          <t>57,91; 93,28</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,03; 39,45</t>
+          <t>7,69; 40,93</t>
         </is>
       </c>
     </row>
@@ -1562,57 +1562,57 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,8; 68,72</t>
+          <t>25,91; 68,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,17</t>
+          <t>0,0; 46,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,07; 61,85</t>
+          <t>12,02; 58,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,49; 62,62</t>
+          <t>21,7; 62,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,36; 46,35</t>
+          <t>12,04; 49,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,88; 50,37</t>
+          <t>6,87; 49,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,88; 54,8</t>
+          <t>14,75; 54,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,94; 40,08</t>
+          <t>10,79; 38,1</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,97; 49,85</t>
+          <t>22,18; 50,48</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,9; 40,25</t>
+          <t>7,83; 37,81</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,54; 48,24</t>
+          <t>17,34; 47,09</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,59; 54,96</t>
+          <t>10,68; 52,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,02; 39,38</t>
+          <t>8,52; 38,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,37; 62,15</t>
+          <t>10,28; 68,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,19; 87,7</t>
+          <t>35,28; 89,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,99; 45,3</t>
+          <t>15,3; 46,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,93; 44,87</t>
+          <t>16,2; 45,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,1; 92,46</t>
+          <t>45,5; 92,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,76; 81,57</t>
+          <t>18,64; 81,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,09; 42,52</t>
+          <t>17,11; 42,14</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15,67; 37,24</t>
+          <t>15,83; 37,29</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32,94; 72,78</t>
+          <t>32,38; 72,19</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>38,33; 78,44</t>
+          <t>37,99; 78,19</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,2; 33,47</t>
+          <t>14,64; 33,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26,84; 43,29</t>
+          <t>26,58; 43,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29,11; 51,45</t>
+          <t>29,7; 52,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27,69; 58,93</t>
+          <t>27,16; 56,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,42; 37,76</t>
+          <t>21,85; 38,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,02; 41,34</t>
+          <t>26,19; 41,52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,37; 56,85</t>
+          <t>35,03; 57,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19,14; 39,3</t>
+          <t>20,14; 40,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,57; 32,23</t>
+          <t>20,38; 33,08</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28,31; 40,06</t>
+          <t>28,71; 40,23</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34,9; 50,98</t>
+          <t>35,99; 52,31</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25,88; 43,54</t>
+          <t>24,71; 42,72</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2565</t>
+          <t>0; 2574</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4021; 9983</t>
+          <t>3973; 10149</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>472; 4129</t>
+          <t>441; 4330</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3600; 12312</t>
+          <t>3523; 12613</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>630; 4633</t>
+          <t>622; 4792</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3326; 10891</t>
+          <t>3705; 10935</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1275; 6016</t>
+          <t>1160; 5986</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>628; 6235</t>
+          <t>629; 5734</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>694; 6016</t>
+          <t>682; 5571</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9740; 19428</t>
+          <t>9494; 19174</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2628; 8559</t>
+          <t>2566; 8520</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5051; 19668</t>
+          <t>5367; 19714</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2438; 7557</t>
+          <t>2506; 7493</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2679; 8009</t>
+          <t>2635; 8052</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1188; 3632</t>
+          <t>1218; 3632</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4127</t>
+          <t>0; 4201</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>641; 4555</t>
+          <t>643; 4611</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2745; 8330</t>
+          <t>2631; 8233</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>626; 3403</t>
+          <t>609; 3403</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1891; 6942</t>
+          <t>2079; 7060</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3587; 10531</t>
+          <t>3757; 10915</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7039; 14706</t>
+          <t>7174; 14701</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2551; 6428</t>
+          <t>2987; 6420</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3131; 9696</t>
+          <t>3089; 9723</t>
         </is>
       </c>
     </row>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3202</t>
+          <t>0; 3129</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>658; 5049</t>
+          <t>636; 4951</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4026</t>
+          <t>0; 3767</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3697</t>
+          <t>471; 3844</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>637; 4069</t>
+          <t>642; 4066</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,27 +2660,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1179; 5944</t>
+          <t>1111; 6111</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>777; 5471</t>
+          <t>786; 5598</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1944; 7500</t>
+          <t>1438; 7683</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3822</t>
+          <t>0; 4378</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2376; 8259</t>
+          <t>2089; 8283</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2385</t>
+          <t>0; 2302</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3588</t>
+          <t>0; 3099</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1114; 5847</t>
+          <t>1306; 6135</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>724; 5572</t>
+          <t>796; 5857</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>606; 4750</t>
+          <t>612; 4756</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3225</t>
+          <t>0; 2980</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1286; 6339</t>
+          <t>1453; 6448</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 6697</t>
+          <t>0; 6464</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>616; 5700</t>
+          <t>681; 5725</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>627; 5251</t>
+          <t>638; 5297</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3931; 10573</t>
+          <t>3955; 10907</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>718; 9881</t>
+          <t>753; 10237</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3295</t>
+          <t>0; 3402</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2071</t>
+          <t>0; 1621</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2544; 7744</t>
+          <t>2718; 7759</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1617; 4151</t>
+          <t>1829; 4151</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1410; 6708</t>
+          <t>1374; 6574</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3296; 9564</t>
+          <t>3304; 9437</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1743; 5887</t>
+          <t>1920; 5792</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3707</t>
+          <t>0; 3708</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2592; 6714</t>
+          <t>3142; 6707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -3269,42 +3269,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3189</t>
+          <t>0; 3206</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>666; 4847</t>
+          <t>659; 4768</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4107; 7957</t>
+          <t>4152; 7957</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1214; 6055</t>
+          <t>1372; 6000</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>715; 5160</t>
+          <t>702; 5196</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1396; 7145</t>
+          <t>1404; 7010</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8145; 14299</t>
+          <t>8871; 14289</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1106; 6205</t>
+          <t>1209; 6438</t>
         </is>
       </c>
     </row>
@@ -3462,57 +3462,57 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3346; 8913</t>
+          <t>3361; 8908</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4080</t>
+          <t>0; 3424</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1166; 5976</t>
+          <t>1161; 5686</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3237; 9433</t>
+          <t>3269; 9358</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2206; 8273</t>
+          <t>2149; 8920</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>632; 4632</t>
+          <t>632; 4590</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3289; 12112</t>
+          <t>3259; 12107</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3217; 9961</t>
+          <t>2680; 9468</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6770; 15363</t>
+          <t>6834; 15557</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1310; 6678</t>
+          <t>1300; 6274</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5890; 15321</t>
+          <t>5508; 14956</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1218; 6320</t>
+          <t>1228; 6038</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1861; 7318</t>
+          <t>1584; 7232</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>770; 4613</t>
+          <t>763; 5062</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2765; 7306</t>
+          <t>2939; 7424</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3425; 10354</t>
+          <t>3497; 10640</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3385; 10172</t>
+          <t>3672; 10281</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3439; 7736</t>
+          <t>3807; 7750</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1512; 6577</t>
+          <t>1503; 6575</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5870; 14606</t>
+          <t>5877; 14477</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6462; 15361</t>
+          <t>6530; 15380</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5201; 11491</t>
+          <t>5113; 11399</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6284; 12858</t>
+          <t>6227; 12817</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>8551; 18823</t>
+          <t>8235; 18927</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>22240; 35877</t>
+          <t>22023; 35934</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13716; 24245</t>
+          <t>13995; 24775</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17385; 37000</t>
+          <t>17052; 35165</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>17885; 31518</t>
+          <t>18238; 31815</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26651; 42342</t>
+          <t>26828; 42523</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17685; 29248</t>
+          <t>18024; 29737</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>18953; 38918</t>
+          <t>19946; 39888</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>28746; 45033</t>
+          <t>28478; 46224</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>52464; 74221</t>
+          <t>53194; 74540</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>34396; 50248</t>
+          <t>35470; 51558</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>41883; 70448</t>
+          <t>39976; 69126</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP09-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP09-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17,87%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40,38%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35,74%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18,45%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>10,27%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>47,74%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>27,66%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>66,33%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,87%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>40,38%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>35,74%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,19</t>
+          <t>5,51; 44,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,1; 69,22</t>
+          <t>20,35; 61,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,37; 62,55</t>
+          <t>12,88; 66,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,63; 95,35</t>
+          <t>0,0; 44,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 42,22</t>
+          <t>0,0; 43,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,73; 61,2</t>
+          <t>26,74; 68,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,91; 66,62</t>
+          <t>7,04; 61,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 41,82</t>
+          <t>17,28; 76,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 32,44</t>
+          <t>3,95; 34,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,18; 58,94</t>
+          <t>30,2; 59,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,13; 53,56</t>
+          <t>15,37; 53,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,92; 73,18</t>
+          <t>14,43; 49,62</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>16,6%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>46,25%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>58,88%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>54,07%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>47,17%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>43,52%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>83,37%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20,79%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>16,6%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>46,25%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>58,88%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,84; 74,29</t>
+          <t>5,43; 38,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,94; 67,03</t>
+          <t>22,34; 69,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,54; 100,0</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,64</t>
+          <t>24,19; 83,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 39,12</t>
+          <t>22,31; 74,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,09; 69,13</t>
+          <t>21,07; 67,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,9; 100,0</t>
+          <t>34,67; 100,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,73; 80,57</t>
+          <t>0,0; 52,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,18; 49,9</t>
+          <t>16,68; 48,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,99; 61,45</t>
+          <t>28,88; 60,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42,45; 91,24</t>
+          <t>36,62; 91,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,78; 59,1</t>
+          <t>17,05; 59,87</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>37,15%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>32,33%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37,84%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>15,44%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>22,87%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>32,85%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22,96%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>37,15%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>32,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,08</t>
+          <t>10,78; 74,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,88; 53,51</t>
+          <t>10,37; 65,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 53,35</t>
+          <t>12,84; 65,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,04; 74,67</t>
+          <t>0,0; 61,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,43; 66,07</t>
+          <t>6,96; 52,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 82,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,08; 71,94</t>
+          <t>8,14; 58,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 55,06</t>
+          <t>7,88; 54,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,33; 49,86</t>
+          <t>9,15; 48,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,42</t>
+          <t>0,0; 57,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,31; 52,76</t>
+          <t>14,93; 55,31</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28,06%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39,28%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7,97%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>36,8%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>37,4%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29,29%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>28,06%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>39,28%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,81</t>
+          <t>8,02; 64,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,48</t>
+          <t>0,0; 40,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,31; 67,23</t>
+          <t>15,43; 70,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,58; 63,08</t>
+          <t>0,0; 35,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 63,61</t>
+          <t>0,0; 35,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,42</t>
+          <t>0,0; 85,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,19; 67,41</t>
+          <t>13,68; 67,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,12</t>
+          <t>9,53; 61,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 40,64</t>
+          <t>4,8; 41,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 44,24</t>
+          <t>5,04; 45,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,16; 58,35</t>
+          <t>20,98; 59,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 32,51</t>
+          <t>4,01; 35,13</t>
         </is>
       </c>
     </row>
@@ -1209,62 +1209,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>43,12%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59,6%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>85,6%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>29,61%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>16,34%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>14,44%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>43,12%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>59,6%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>36,13%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>43,63%</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>85,83%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>36,13%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>43,63%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,55%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14,29; 85,66</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>31,35; 84,92</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>40,8; 100,0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 73,65</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 63,53</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 61,53</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 50,65</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14,29; 85,67</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29,7; 84,8</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 67,35</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>13,76; 65,47</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>22,94; 65,84</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>44,05; 100,0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>13,58; 64,95</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>22,78; 65,06</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,12; 78,79</t>
+          <t>26,82; 79,39</t>
         </is>
       </c>
     </row>
@@ -1349,44 +1349,44 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>25,37%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22,77%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>86,81%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28,9%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>67,71%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>25,46%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>71,5%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>25,37%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>22,77%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>86,81%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>27,87%</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t>37,77%</t>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 63,25</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7,38; 53,11</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>42,3; 100,0</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>11,18; 54,2</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 63,71</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>42,68; 91,11</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 63,58</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>37,03; 91,21</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 63,92</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>7,28; 52,62</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>52,18; 100,0</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>11,88; 51,95</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,9; 73,26</t>
+          <t>9,98; 66,19</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,43; 47,1</t>
+          <t>9,41; 47,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57,91; 93,28</t>
+          <t>55,44; 93,25</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,69; 40,93</t>
+          <t>7,42; 40,61</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>39,65%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>27,28%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>21,59%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>32,18%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>47,35%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>18,12%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>32,1%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>39,65%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>27,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,59%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>21,58; 60,13</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11,06; 47,95</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6,77; 51,21</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14,83; 55,14</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>25,91; 68,68</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 46,3</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>12,02; 58,85</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>21,7; 62,12</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,04; 49,97</t>
+          <t>25,85; 68,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,87; 49,91</t>
+          <t>0,0; 57,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,75; 54,78</t>
+          <t>11,33; 59,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,79; 38,1</t>
+          <t>13,06; 40,59</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22,18; 50,48</t>
+          <t>23,19; 51,21</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,83; 37,81</t>
+          <t>7,92; 39,54</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,34; 47,09</t>
+          <t>17,92; 47,23</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>29,46%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>28,65%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>70,63%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>48,85%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>27,58%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>21,55%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>34,86%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>67,11%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>29,46%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>28,65%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>70,63%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,94%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,68; 52,51</t>
+          <t>14,7; 46,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,52; 38,92</t>
+          <t>16,47; 47,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,28; 68,19</t>
+          <t>39,88; 92,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35,28; 89,13</t>
+          <t>17,97; 79,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,3; 46,55</t>
+          <t>10,31; 52,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,2; 45,35</t>
+          <t>9,35; 39,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,5; 92,63</t>
+          <t>10,53; 62,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,64; 81,54</t>
+          <t>36,06; 89,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,11; 42,14</t>
+          <t>17,19; 42,51</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15,83; 37,29</t>
+          <t>15,83; 37,74</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32,38; 72,19</t>
+          <t>34,38; 72,43</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>37,99; 78,19</t>
+          <t>36,96; 77,7</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>28,8%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>33,44%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>46,21%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>31,15%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>22,76%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>34,27%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>40,48%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>38,07%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>33,44%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>46,21%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14,64; 33,65</t>
+          <t>21,67; 36,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26,58; 43,36</t>
+          <t>26,05; 42,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29,7; 52,57</t>
+          <t>35,37; 58,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27,16; 56,01</t>
+          <t>19,96; 40,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,85; 38,11</t>
+          <t>14,34; 32,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,19; 41,52</t>
+          <t>26,05; 42,84</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,03; 57,8</t>
+          <t>29,68; 52,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20,14; 40,28</t>
+          <t>22,96; 42,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,38; 33,08</t>
+          <t>20,95; 33,06</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28,71; 40,23</t>
+          <t>28,93; 40,34</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35,99; 52,31</t>
+          <t>35,85; 52,0</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24,71; 42,72</t>
+          <t>24,58; 39,54</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7216</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3212</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2130</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>6999</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1914</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8775</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7216</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3212</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11253</t>
+          <t>5620</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2574</t>
+          <t>625; 5018</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3973; 10149</t>
+          <t>3636; 10933</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>441; 4330</t>
+          <t>1157; 5950</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3523; 12613</t>
+          <t>0; 5144</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>622; 4792</t>
+          <t>0; 2541</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3705; 10935</t>
+          <t>3920; 10037</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1160; 5986</t>
+          <t>487; 4237</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>629; 5734</t>
+          <t>1336; 5918</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>682; 5571</t>
+          <t>678; 5887</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9494; 19174</t>
+          <t>9825; 19329</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2566; 8520</t>
+          <t>2445; 8469</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5367; 19714</t>
+          <t>2783; 9565</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1957</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5509</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4047</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4757</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5228</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3028</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5509</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>5553</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2506; 7493</t>
+          <t>640; 4578</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2635; 8052</t>
+          <t>2661; 8282</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1218; 3632</t>
+          <t>0; 3403</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4201</t>
+          <t>1811; 6234</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>643; 4611</t>
+          <t>2251; 7554</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2631; 8233</t>
+          <t>2532; 8056</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>609; 3403</t>
+          <t>1259; 3632</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2079; 7060</t>
+          <t>0; 4116</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3757; 10915</t>
+          <t>3649; 10578</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7174; 14701</t>
+          <t>6909; 14584</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2987; 6420</t>
+          <t>2576; 6424</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3089; 9723</t>
+          <t>2618; 9192</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1874</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2765</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>791</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2116</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1530</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1654</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1874</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>4491</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3129</t>
+          <t>544; 3774</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>636; 4951</t>
+          <t>638; 4042</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3767</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>471; 3844</t>
+          <t>938; 4793</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>607; 3767</t>
+          <t>0; 3164</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>642; 4066</t>
+          <t>644; 4901</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3835</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1111; 6111</t>
+          <t>536; 3835</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>786; 5598</t>
+          <t>801; 5565</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1438; 7683</t>
+          <t>1410; 7527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4378</t>
+          <t>0; 4231</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2089; 8283</t>
+          <t>2074; 7687</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3757</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1552</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>3413</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2720</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3757</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>4681</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2302</t>
+          <t>600; 4813</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3099</t>
+          <t>0; 3177</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1306; 6135</t>
+          <t>1476; 6723</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>796; 5857</t>
+          <t>0; 6825</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>612; 4756</t>
+          <t>0; 2322</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2980</t>
+          <t>0; 3606</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1453; 6448</t>
+          <t>1248; 6161</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 6464</t>
+          <t>964; 6272</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>681; 5725</t>
+          <t>677; 5891</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>638; 5297</t>
+          <t>603; 5416</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3955; 10907</t>
+          <t>3922; 11204</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>753; 10237</t>
+          <t>1185; 10375</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,62 +2973,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5453</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3540</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1551</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>875</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>462</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5453</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3657</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>6328</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3563</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3657</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>6328</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>4078</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>698; 4184</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2869; 7771</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1687; 4135</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>0; 3857</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0; 3402</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3295</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0; 1621</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>698; 4185</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2718; 7759</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2250</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1393; 6627</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3328; 9550</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1829; 4151</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1374; 6574</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>3304; 9437</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1920; 5792</t>
+          <t>2005; 5935</t>
         </is>
       </c>
     </row>
@@ -3118,37 +3118,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,44 +3181,44 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1273</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2063</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6907</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2777</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1406</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1482</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>5264</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1273</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2063</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>6907</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3219</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
           <t>2678</t>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>2777</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>0; 3173</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>669; 4813</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>3366; 7957</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1074; 5208</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>0; 2076</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3708</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>3142; 6707</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3701</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2727; 6715</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3206</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>659; 4768</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>4152; 7957</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>1372; 6000</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>702; 5196</t>
+          <t>708; 4694</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1404; 7010</t>
+          <t>1401; 7127</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8871; 14289</t>
+          <t>8493; 14285</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1209; 6438</t>
+          <t>1045; 5720</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,49 +3389,49 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>5973</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>4870</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>6781</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>6141</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>1340</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>3101</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>3036</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>5973</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>4870</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>6836</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>5973</t>
-        </is>
-      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t>11011</t>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>9937</t>
+          <t>9817</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>3251; 9057</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1974; 8559</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>622; 4710</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>3125; 11617</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>3361; 8908</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0; 3424</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1161; 5686</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>3269; 9358</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2149; 8920</t>
+          <t>3352; 8914</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>632; 4590</t>
+          <t>0; 4222</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3259; 12107</t>
+          <t>1117; 5890</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2680; 9468</t>
+          <t>3246; 10087</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6834; 15557</t>
+          <t>7147; 15782</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1300; 6274</t>
+          <t>1313; 6559</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5508; 14956</t>
+          <t>5543; 14611</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>6733</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6495</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>5910</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4059</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>3171</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>4004</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>2587</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5591</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>6733</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>6495</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>5910</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>9775</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1228; 6038</t>
+          <t>3360; 10713</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1584; 7232</t>
+          <t>3734; 10673</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>763; 5062</t>
+          <t>3337; 7751</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2939; 7424</t>
+          <t>1493; 6642</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3497; 10640</t>
+          <t>1185; 6023</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3672; 10281</t>
+          <t>1737; 7422</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3807; 7750</t>
+          <t>781; 4617</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1503; 6575</t>
+          <t>2984; 7378</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5877; 14477</t>
+          <t>5905; 14605</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6530; 15380</t>
+          <t>6531; 15566</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5113; 11399</t>
+          <t>5428; 11437</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6227; 12817</t>
+          <t>6130; 12886</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>24042</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>34252</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>23775</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>27682</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>12800</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>28397</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>19077</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>23901</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>24042</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>34252</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>23775</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>29601</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>53502</t>
+          <t>46792</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>8235; 18927</t>
+          <t>18092; 30739</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>22023; 35934</t>
+          <t>26680; 43680</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13995; 24775</t>
+          <t>18195; 29911</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17052; 35165</t>
+          <t>17739; 36240</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>18238; 31815</t>
+          <t>8067; 18237</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26828; 42523</t>
+          <t>21589; 35499</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18024; 29737</t>
+          <t>13988; 24681</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>19946; 39888</t>
+          <t>13376; 24933</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>28478; 46224</t>
+          <t>29266; 46196</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>53194; 74540</t>
+          <t>53598; 74753</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>35470; 51558</t>
+          <t>35337; 51256</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>39976; 69126</t>
+          <t>36173; 58177</t>
         </is>
       </c>
     </row>
